--- a/Master- To Do.xlsx
+++ b/Master- To Do.xlsx
@@ -9,11 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="5475" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="5475" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Reading" sheetId="1" r:id="rId1"/>
     <sheet name="Leetcode" sheetId="2" r:id="rId2"/>
+    <sheet name="Python Node" sheetId="4" r:id="rId3"/>
+    <sheet name="Java" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="257">
   <si>
     <t>Building Secure and Reliable Systems</t>
   </si>
@@ -367,6 +369,435 @@
   </si>
   <si>
     <t xml:space="preserve">Word Search </t>
+  </si>
+  <si>
+    <t>Python Tutorial</t>
+  </si>
+  <si>
+    <t>Video 1</t>
+  </si>
+  <si>
+    <t>Video 34</t>
+  </si>
+  <si>
+    <t>Video 67</t>
+  </si>
+  <si>
+    <t>Video 100</t>
+  </si>
+  <si>
+    <t>Video 133</t>
+  </si>
+  <si>
+    <t>Video 2</t>
+  </si>
+  <si>
+    <t>Video 35</t>
+  </si>
+  <si>
+    <t>Video 68</t>
+  </si>
+  <si>
+    <t>Video 101</t>
+  </si>
+  <si>
+    <t>Video 134</t>
+  </si>
+  <si>
+    <t>Video 3</t>
+  </si>
+  <si>
+    <t>Video 36</t>
+  </si>
+  <si>
+    <t>Video 69</t>
+  </si>
+  <si>
+    <t>Video 102</t>
+  </si>
+  <si>
+    <t>Video 4</t>
+  </si>
+  <si>
+    <t>Video 37</t>
+  </si>
+  <si>
+    <t>Video 70</t>
+  </si>
+  <si>
+    <t>Video 103</t>
+  </si>
+  <si>
+    <t>Video 5</t>
+  </si>
+  <si>
+    <t>Video 38</t>
+  </si>
+  <si>
+    <t>Video 71</t>
+  </si>
+  <si>
+    <t>Video 104</t>
+  </si>
+  <si>
+    <t>Video 6</t>
+  </si>
+  <si>
+    <t>Video 39</t>
+  </si>
+  <si>
+    <t>Video 72</t>
+  </si>
+  <si>
+    <t>Video 105</t>
+  </si>
+  <si>
+    <t>Video 7</t>
+  </si>
+  <si>
+    <t>Video 40</t>
+  </si>
+  <si>
+    <t>Video 73</t>
+  </si>
+  <si>
+    <t>Video 106</t>
+  </si>
+  <si>
+    <t>Video 8</t>
+  </si>
+  <si>
+    <t>Video 41</t>
+  </si>
+  <si>
+    <t>Video 74</t>
+  </si>
+  <si>
+    <t>Video 107</t>
+  </si>
+  <si>
+    <t>Video 9</t>
+  </si>
+  <si>
+    <t>Video 42</t>
+  </si>
+  <si>
+    <t>Video 75</t>
+  </si>
+  <si>
+    <t>Video 108</t>
+  </si>
+  <si>
+    <t>Video 10</t>
+  </si>
+  <si>
+    <t>Video 43</t>
+  </si>
+  <si>
+    <t>Video 76</t>
+  </si>
+  <si>
+    <t>Video 109</t>
+  </si>
+  <si>
+    <t>Video 11</t>
+  </si>
+  <si>
+    <t>Video 44</t>
+  </si>
+  <si>
+    <t>Video 77</t>
+  </si>
+  <si>
+    <t>Video 110</t>
+  </si>
+  <si>
+    <t>Video 12</t>
+  </si>
+  <si>
+    <t>Video 45</t>
+  </si>
+  <si>
+    <t>Video 78</t>
+  </si>
+  <si>
+    <t>Video 111</t>
+  </si>
+  <si>
+    <t>Video 13</t>
+  </si>
+  <si>
+    <t>Video 46</t>
+  </si>
+  <si>
+    <t>Video 79</t>
+  </si>
+  <si>
+    <t>Video 112</t>
+  </si>
+  <si>
+    <t>Video 14</t>
+  </si>
+  <si>
+    <t>Video 47</t>
+  </si>
+  <si>
+    <t>Video 80</t>
+  </si>
+  <si>
+    <t>Video 113</t>
+  </si>
+  <si>
+    <t>Video 15</t>
+  </si>
+  <si>
+    <t>Video 48</t>
+  </si>
+  <si>
+    <t>Video 81</t>
+  </si>
+  <si>
+    <t>Video 114</t>
+  </si>
+  <si>
+    <t>Video 16</t>
+  </si>
+  <si>
+    <t>Video 49</t>
+  </si>
+  <si>
+    <t>Video 82</t>
+  </si>
+  <si>
+    <t>Video 115</t>
+  </si>
+  <si>
+    <t>Video 17</t>
+  </si>
+  <si>
+    <t>Video 50</t>
+  </si>
+  <si>
+    <t>Video 83</t>
+  </si>
+  <si>
+    <t>Video 116</t>
+  </si>
+  <si>
+    <t>Video 18</t>
+  </si>
+  <si>
+    <t>Video 51</t>
+  </si>
+  <si>
+    <t>Video 84</t>
+  </si>
+  <si>
+    <t>Video 117</t>
+  </si>
+  <si>
+    <t>Video 19</t>
+  </si>
+  <si>
+    <t>Video 52</t>
+  </si>
+  <si>
+    <t>Video 85</t>
+  </si>
+  <si>
+    <t>Video 118</t>
+  </si>
+  <si>
+    <t>Video 20</t>
+  </si>
+  <si>
+    <t>Video 53</t>
+  </si>
+  <si>
+    <t>Video 86</t>
+  </si>
+  <si>
+    <t>Video 119</t>
+  </si>
+  <si>
+    <t>Video 21</t>
+  </si>
+  <si>
+    <t>Video 54</t>
+  </si>
+  <si>
+    <t>Video 87</t>
+  </si>
+  <si>
+    <t>Video 120</t>
+  </si>
+  <si>
+    <t>Video 22</t>
+  </si>
+  <si>
+    <t>Video 55</t>
+  </si>
+  <si>
+    <t>Video 88</t>
+  </si>
+  <si>
+    <t>Video 121</t>
+  </si>
+  <si>
+    <t>Video 23</t>
+  </si>
+  <si>
+    <t>Video 56</t>
+  </si>
+  <si>
+    <t>Video 89</t>
+  </si>
+  <si>
+    <t>Video 122</t>
+  </si>
+  <si>
+    <t>Video 24</t>
+  </si>
+  <si>
+    <t>Video 57</t>
+  </si>
+  <si>
+    <t>Video 90</t>
+  </si>
+  <si>
+    <t>Video 123</t>
+  </si>
+  <si>
+    <t>Video 25</t>
+  </si>
+  <si>
+    <t>Video 58</t>
+  </si>
+  <si>
+    <t>Video 91</t>
+  </si>
+  <si>
+    <t>Video 124</t>
+  </si>
+  <si>
+    <t>Video 26</t>
+  </si>
+  <si>
+    <t>Video 59</t>
+  </si>
+  <si>
+    <t>Video 92</t>
+  </si>
+  <si>
+    <t>Video 125</t>
+  </si>
+  <si>
+    <t>Video 27</t>
+  </si>
+  <si>
+    <t>Video 60</t>
+  </si>
+  <si>
+    <t>Video 93</t>
+  </si>
+  <si>
+    <t>Video 126</t>
+  </si>
+  <si>
+    <t>Video 28</t>
+  </si>
+  <si>
+    <t>Video 61</t>
+  </si>
+  <si>
+    <t>Video 94</t>
+  </si>
+  <si>
+    <t>Video 127</t>
+  </si>
+  <si>
+    <t>Video 29</t>
+  </si>
+  <si>
+    <t>Video 62</t>
+  </si>
+  <si>
+    <t>Video 95</t>
+  </si>
+  <si>
+    <t>Video 128</t>
+  </si>
+  <si>
+    <t>Video 30</t>
+  </si>
+  <si>
+    <t>Video 63</t>
+  </si>
+  <si>
+    <t>Video 96</t>
+  </si>
+  <si>
+    <t>Video 129</t>
+  </si>
+  <si>
+    <t>Video 31</t>
+  </si>
+  <si>
+    <t>Video 64</t>
+  </si>
+  <si>
+    <t>Video 97</t>
+  </si>
+  <si>
+    <t>Video 130</t>
+  </si>
+  <si>
+    <t>Video 32</t>
+  </si>
+  <si>
+    <t>Video 65</t>
+  </si>
+  <si>
+    <t>Video 98</t>
+  </si>
+  <si>
+    <t>Video 131</t>
+  </si>
+  <si>
+    <t>Video 33</t>
+  </si>
+  <si>
+    <t>Video 66</t>
+  </si>
+  <si>
+    <t>Video 99</t>
+  </si>
+  <si>
+    <t>Video 132</t>
+  </si>
+  <si>
+    <t>Node.js (Net Ninja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node.js Crash Course </t>
+  </si>
+  <si>
+    <t>Java Tutorial- Caleb</t>
+  </si>
+  <si>
+    <t>Java Tutorial- Derek</t>
+  </si>
+  <si>
+    <t>Basics 1</t>
+  </si>
+  <si>
+    <t>Basics 2</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>Java Tutorial- Alex</t>
   </si>
 </sst>
 </file>
@@ -534,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -596,6 +1027,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1708,4 +2144,1704 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" customWidth="1"/>
+    <col min="7" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" customWidth="1"/>
+    <col min="10" max="11" width="10.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="G1" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="H1" s="27"/>
+      <c r="J1" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="K1" s="27"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="G4" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="G5" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="G6" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="J6" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="G7" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="J7" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="G8" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="J8" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="G9" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="J9" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="G10" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="J10" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="G11" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="J11" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="G12" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="J12" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="G13" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="J13" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" s="29"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="G14" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="G15" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="G16" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="G17" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="G18" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="G19" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="G20" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="G21" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="G22" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="G23" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="G24" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="G25" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="G26" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="G27" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="G28" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="G29" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="G30" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="G31" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="G32" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="G33" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="E34" s="29"/>
+      <c r="G34" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="H34" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="F1" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="J1" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="F4" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="F5" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="L5" s="28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="F6" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="F7" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="K7" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="L7" s="28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="F8" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="K8" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="F9" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="L9" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="F10" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="F11" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="F12" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="F13" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="K13" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="L13" s="28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="F14" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="F15" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="L15" s="28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="F16" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="F17" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="K17" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="L17" s="28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="F18" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="F19" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="K19" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="L19" s="28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="F20" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="J20" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="K20" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" s="28" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="F21" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="K21" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="L21" s="28" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="F22" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="J22" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="K22" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="L22" s="28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="F23" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="K23" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="L23" s="28" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="F24" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="K24" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="L24" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="F25" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="K25" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="L25" s="28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="F26" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="K26" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="L26" s="28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="F27" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="K27" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="L27" s="28" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="F28" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="L28" s="28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="F29" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="F30" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="F31" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="F32" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="F33" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" s="29"/>
+      <c r="F34" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="H34" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Master- To Do.xlsx
+++ b/Master- To Do.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="5475" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="5475" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Reading" sheetId="1" r:id="rId1"/>
     <sheet name="Leetcode" sheetId="2" r:id="rId2"/>
     <sheet name="Python Node" sheetId="4" r:id="rId3"/>
     <sheet name="Java" sheetId="6" r:id="rId4"/>
+    <sheet name="Career" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1027,11 +1028,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2159,708 +2160,708 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="G1" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="H1" s="27"/>
-      <c r="J1" s="27" t="s">
+      <c r="H1" s="29"/>
+      <c r="J1" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="K1" s="27"/>
+      <c r="K1" s="29"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="27" t="s">
         <v>115</v>
       </c>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="27" t="s">
         <v>120</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="27" t="s">
         <v>128</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="27" t="s">
         <v>125</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="27" t="s">
         <v>132</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="J5" s="27" t="s">
         <v>129</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="27" t="s">
         <v>136</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="27" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="5"/>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="27" t="s">
         <v>133</v>
       </c>
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="27" t="s">
         <v>140</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="27" t="s">
         <v>137</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="27" t="s">
         <v>137</v>
       </c>
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="27" t="s">
         <v>144</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="27" t="s">
         <v>141</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="27" t="s">
         <v>141</v>
       </c>
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="27" t="s">
         <v>148</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="27" t="s">
         <v>145</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="27" t="s">
         <v>145</v>
       </c>
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="27" t="s">
         <v>152</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="27" t="s">
         <v>149</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="27" t="s">
         <v>149</v>
       </c>
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="27" t="s">
         <v>156</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="27" t="s">
         <v>153</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="J11" s="28" t="s">
+      <c r="J11" s="27" t="s">
         <v>153</v>
       </c>
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="27" t="s">
         <v>160</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="27" t="s">
         <v>157</v>
       </c>
       <c r="H12" s="6"/>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="27" t="s">
         <v>157</v>
       </c>
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="27" t="s">
         <v>164</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="27" t="s">
         <v>161</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="K13" s="29"/>
+      <c r="K13" s="28"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="27" t="s">
         <v>168</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="27" t="s">
         <v>165</v>
       </c>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="27" t="s">
         <v>172</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="G15" s="28" t="s">
+      <c r="G15" s="27" t="s">
         <v>169</v>
       </c>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="27" t="s">
         <v>176</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="G16" s="28" t="s">
+      <c r="G16" s="27" t="s">
         <v>173</v>
       </c>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>180</v>
       </c>
       <c r="E17" s="6"/>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="27" t="s">
         <v>177</v>
       </c>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="27" t="s">
         <v>184</v>
       </c>
       <c r="E18" s="6"/>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="27" t="s">
         <v>181</v>
       </c>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="27" t="s">
         <v>188</v>
       </c>
       <c r="E19" s="6"/>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="27" t="s">
         <v>185</v>
       </c>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E20" s="6"/>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="27" t="s">
         <v>189</v>
       </c>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="27" t="s">
         <v>196</v>
       </c>
       <c r="E21" s="6"/>
-      <c r="G21" s="28" t="s">
+      <c r="G21" s="27" t="s">
         <v>193</v>
       </c>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="27" t="s">
         <v>200</v>
       </c>
       <c r="E22" s="6"/>
-      <c r="G22" s="28" t="s">
+      <c r="G22" s="27" t="s">
         <v>197</v>
       </c>
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="27" t="s">
         <v>204</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="G23" s="28" t="s">
+      <c r="G23" s="27" t="s">
         <v>201</v>
       </c>
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="27" t="s">
         <v>208</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="G24" s="28" t="s">
+      <c r="G24" s="27" t="s">
         <v>205</v>
       </c>
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="27" t="s">
         <v>212</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="G25" s="28" t="s">
+      <c r="G25" s="27" t="s">
         <v>209</v>
       </c>
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="27" t="s">
         <v>216</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="G26" s="28" t="s">
+      <c r="G26" s="27" t="s">
         <v>213</v>
       </c>
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="27" t="s">
         <v>220</v>
       </c>
       <c r="E27" s="6"/>
-      <c r="G27" s="28" t="s">
+      <c r="G27" s="27" t="s">
         <v>217</v>
       </c>
       <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="27" t="s">
         <v>224</v>
       </c>
       <c r="E28" s="6"/>
-      <c r="G28" s="28" t="s">
+      <c r="G28" s="27" t="s">
         <v>221</v>
       </c>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="27" t="s">
         <v>228</v>
       </c>
       <c r="E29" s="6"/>
-      <c r="G29" s="28" t="s">
+      <c r="G29" s="27" t="s">
         <v>225</v>
       </c>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="27" t="s">
         <v>232</v>
       </c>
       <c r="E30" s="6"/>
-      <c r="G30" s="28" t="s">
+      <c r="G30" s="27" t="s">
         <v>229</v>
       </c>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="27" t="s">
         <v>236</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="27" t="s">
         <v>233</v>
       </c>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="27" t="s">
         <v>240</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="27" t="s">
         <v>237</v>
       </c>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="27" t="s">
         <v>244</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="G33" s="28" t="s">
+      <c r="G33" s="27" t="s">
         <v>241</v>
       </c>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="E34" s="29"/>
-      <c r="G34" s="28" t="s">
+      <c r="E34" s="28"/>
+      <c r="G34" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="H34" s="29"/>
+      <c r="H34" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2885,955 +2886,955 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="F1" s="27" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="F1" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="J1" s="27" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="J1" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="27" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="L3" s="28" t="s">
+      <c r="L3" s="27" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>127</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="27" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="27" t="s">
         <v>131</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="J5" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="K5" s="28" t="s">
+      <c r="K5" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="L5" s="28" t="s">
+      <c r="L5" s="27" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="27" t="s">
         <v>135</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L6" s="27" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="27" t="s">
         <v>139</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="K7" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="27" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>143</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="K8" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="L8" s="28" t="s">
+      <c r="L8" s="27" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="27" t="s">
         <v>147</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="K9" s="28" t="s">
+      <c r="K9" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L9" s="28" t="s">
+      <c r="L9" s="27" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="27" t="s">
         <v>151</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="L10" s="28" t="s">
+      <c r="L10" s="27" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>155</v>
       </c>
       <c r="D11" s="6"/>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="J11" s="28" t="s">
+      <c r="J11" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="K11" s="28" t="s">
+      <c r="K11" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="L11" s="28" t="s">
+      <c r="L11" s="27" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="27" t="s">
         <v>159</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="K12" s="28" t="s">
+      <c r="K12" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="L12" s="28" t="s">
+      <c r="L12" s="27" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>163</v>
       </c>
       <c r="D13" s="6"/>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="K13" s="28" t="s">
+      <c r="K13" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="L13" s="28" t="s">
+      <c r="L13" s="27" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>167</v>
       </c>
       <c r="D14" s="6"/>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="J14" s="28" t="s">
+      <c r="J14" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="K14" s="28" t="s">
+      <c r="K14" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="L14" s="28" t="s">
+      <c r="L14" s="27" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>171</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="G15" s="28" t="s">
+      <c r="G15" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="H15" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="J15" s="28" t="s">
+      <c r="J15" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="K15" s="28" t="s">
+      <c r="K15" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="L15" s="28" t="s">
+      <c r="L15" s="27" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>175</v>
       </c>
       <c r="D16" s="6"/>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="28" t="s">
+      <c r="G16" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="H16" s="28" t="s">
+      <c r="H16" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="J16" s="28" t="s">
+      <c r="J16" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="K16" s="28" t="s">
+      <c r="K16" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="L16" s="28" t="s">
+      <c r="L16" s="27" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="27" t="s">
         <v>179</v>
       </c>
       <c r="D17" s="6"/>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="H17" s="28" t="s">
+      <c r="H17" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="J17" s="28" t="s">
+      <c r="J17" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="K17" s="28" t="s">
+      <c r="K17" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="L17" s="28" t="s">
+      <c r="L17" s="27" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="27" t="s">
         <v>183</v>
       </c>
       <c r="D18" s="6"/>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="J18" s="28" t="s">
+      <c r="J18" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="K18" s="28" t="s">
+      <c r="K18" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="L18" s="28" t="s">
+      <c r="L18" s="27" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="27" t="s">
         <v>187</v>
       </c>
       <c r="D19" s="6"/>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="J19" s="28" t="s">
+      <c r="J19" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="K19" s="28" t="s">
+      <c r="K19" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="28" t="s">
+      <c r="L19" s="27" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>191</v>
       </c>
       <c r="D20" s="6"/>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="H20" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="J20" s="28" t="s">
+      <c r="J20" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="K20" s="28" t="s">
+      <c r="K20" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="L20" s="28" t="s">
+      <c r="L20" s="27" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="27" t="s">
         <v>195</v>
       </c>
       <c r="D21" s="6"/>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="G21" s="28" t="s">
+      <c r="G21" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="H21" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="J21" s="28" t="s">
+      <c r="J21" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="K21" s="28" t="s">
+      <c r="K21" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="L21" s="28" t="s">
+      <c r="L21" s="27" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="27" t="s">
         <v>199</v>
       </c>
       <c r="D22" s="6"/>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="G22" s="28" t="s">
+      <c r="G22" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="H22" s="28" t="s">
+      <c r="H22" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="J22" s="28" t="s">
+      <c r="J22" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="K22" s="28" t="s">
+      <c r="K22" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="L22" s="28" t="s">
+      <c r="L22" s="27" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>203</v>
       </c>
       <c r="D23" s="6"/>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="G23" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="H23" s="28" t="s">
+      <c r="H23" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="J23" s="28" t="s">
+      <c r="J23" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="K23" s="28" t="s">
+      <c r="K23" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="L23" s="28" t="s">
+      <c r="L23" s="27" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="27" t="s">
         <v>207</v>
       </c>
       <c r="D24" s="6"/>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="G24" s="28" t="s">
+      <c r="G24" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="H24" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="J24" s="28" t="s">
+      <c r="J24" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="K24" s="28" t="s">
+      <c r="K24" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="L24" s="28" t="s">
+      <c r="L24" s="27" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>211</v>
       </c>
       <c r="D25" s="6"/>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="G25" s="28" t="s">
+      <c r="G25" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="H25" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="J25" s="28" t="s">
+      <c r="J25" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="K25" s="28" t="s">
+      <c r="K25" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="L25" s="28" t="s">
+      <c r="L25" s="27" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>215</v>
       </c>
       <c r="D26" s="6"/>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="G26" s="28" t="s">
+      <c r="G26" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="J26" s="28" t="s">
+      <c r="J26" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="K26" s="28" t="s">
+      <c r="K26" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="L26" s="28" t="s">
+      <c r="L26" s="27" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>219</v>
       </c>
       <c r="D27" s="6"/>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="G27" s="28" t="s">
+      <c r="G27" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="J27" s="28" t="s">
+      <c r="J27" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="K27" s="28" t="s">
+      <c r="K27" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="L27" s="28" t="s">
+      <c r="L27" s="27" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>223</v>
       </c>
       <c r="D28" s="6"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="G28" s="28" t="s">
+      <c r="G28" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28" t="s">
+      <c r="J28" s="27"/>
+      <c r="K28" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="L28" s="28" t="s">
+      <c r="L28" s="27" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>227</v>
       </c>
       <c r="D29" s="6"/>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="G29" s="28" t="s">
+      <c r="G29" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28" t="s">
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="27" t="s">
         <v>231</v>
       </c>
       <c r="D30" s="6"/>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="G30" s="28" t="s">
+      <c r="G30" s="27" t="s">
         <v>230</v>
       </c>
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>235</v>
       </c>
       <c r="D31" s="6"/>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="27" t="s">
         <v>234</v>
       </c>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>239</v>
       </c>
       <c r="D32" s="6"/>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="27" t="s">
         <v>238</v>
       </c>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="27" t="s">
         <v>243</v>
       </c>
       <c r="D33" s="6"/>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="G33" s="28" t="s">
+      <c r="G33" s="27" t="s">
         <v>242</v>
       </c>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="D34" s="29"/>
-      <c r="F34" s="28" t="s">
+      <c r="D34" s="28"/>
+      <c r="F34" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="G34" s="28" t="s">
+      <c r="G34" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="H34" s="29"/>
+      <c r="H34" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3844,4 +3845,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Master- To Do.xlsx
+++ b/Master- To Do.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="284">
   <si>
     <t>Building Secure and Reliable Systems</t>
   </si>
@@ -827,6 +827,61 @@
   </si>
   <si>
     <t>Express JS Crash Course</t>
+  </si>
+  <si>
+    <t>Traversy Media (Node.js)</t>
+  </si>
+  <si>
+    <t>Node.js Crash Course</t>
+  </si>
+  <si>
+    <t>Node.js With Passport Authentication</t>
+  </si>
+  <si>
+    <t>Node.js API Authentication With JWT</t>
+  </si>
+  <si>
+    <t>Full Node.js Deployment - NGINX, SSL With Lets Encrypt</t>
+  </si>
+  <si>
+    <t>Using MySQL With Node.js</t>
+  </si>
+  <si>
+    <t>Intro To The Node.js PayPal REST SDK</t>
+  </si>
+  <si>
+    <t>Node.js &amp; Stripe API - Ebook Sales App &amp; Heroku Deploy</t>
+  </si>
+  <si>
+    <t>Nodemailer - Send Emails From Your Node.js App</t>
+  </si>
+  <si>
+    <t>Push Notifications Using Node.js &amp; Service Worker</t>
+  </si>
+  <si>
+    <t>TypeScript Setup With Node &amp; Express</t>
+  </si>
+  <si>
+    <t>Build A Node.js &amp; Redis App From Scratch</t>
+  </si>
+  <si>
+    <t>RESTful API From Scratch Using Node, Express and MongoDB</t>
+  </si>
+  <si>
+    <t>Build a Custom URL Shortener Service</t>
+  </si>
+  <si>
+    <t>Node.js &amp; Express API | Expense Tracker</t>
+  </si>
+  <si>
+    <t>Node.js &amp; Express API | Expense Tracker Part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Realtime Chat With Users &amp; Rooms - Socket.io, Node &amp; Express</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real-Time Tweets &amp; Socket.io </t>
   </si>
 </sst>
 </file>
@@ -994,7 +1049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1058,6 +1113,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2191,21 +2249,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="G1" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="J1" s="30" t="s">
+      <c r="H1" s="31"/>
+      <c r="J1" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="K1" s="30"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -2917,22 +2975,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="F1" s="30" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="F1" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="J1" s="30" t="s">
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="J1" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -3880,65 +3938,142 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C1" s="30" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="27"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="27"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="27"/>
+      <c r="C12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="23" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>274</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Master- To Do.xlsx
+++ b/Master- To Do.xlsx
@@ -9,15 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="5475" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="5475" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Reading" sheetId="1" r:id="rId1"/>
     <sheet name="Leetcode" sheetId="2" r:id="rId2"/>
     <sheet name="Python Node" sheetId="4" r:id="rId3"/>
     <sheet name="Java" sheetId="6" r:id="rId4"/>
-    <sheet name="Tutorial" sheetId="9" r:id="rId5"/>
-    <sheet name="Career" sheetId="7" r:id="rId6"/>
+    <sheet name="JavaScript" sheetId="11" r:id="rId5"/>
+    <sheet name="Tutorial" sheetId="9" r:id="rId6"/>
+    <sheet name="Career" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="318">
   <si>
     <t>Building Secure and Reliable Systems</t>
   </si>
@@ -829,9 +830,6 @@
     <t>Express JS Crash Course</t>
   </si>
   <si>
-    <t>Traversy Media (Node.js)</t>
-  </si>
-  <si>
     <t>Node.js Crash Course</t>
   </si>
   <si>
@@ -865,9 +863,6 @@
     <t>Build A Node.js &amp; Redis App From Scratch</t>
   </si>
   <si>
-    <t>RESTful API From Scratch Using Node, Express and MongoDB</t>
-  </si>
-  <si>
     <t>Build a Custom URL Shortener Service</t>
   </si>
   <si>
@@ -877,11 +872,118 @@
     <t>Node.js &amp; Express API | Expense Tracker Part 2</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Realtime Chat With Users &amp; Rooms - Socket.io, Node &amp; Express</t>
-  </si>
-  <si>
     <t xml:space="preserve">Real-Time Tweets &amp; Socket.io </t>
+  </si>
+  <si>
+    <t>MDN</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>Grammar and types</t>
+  </si>
+  <si>
+    <t>Control flow and error handling</t>
+  </si>
+  <si>
+    <t>Loops and iteration</t>
+  </si>
+  <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>Expressions and operators</t>
+  </si>
+  <si>
+    <t>Numbers and dates</t>
+  </si>
+  <si>
+    <t>Text formatting</t>
+  </si>
+  <si>
+    <t>Regular expressions</t>
+  </si>
+  <si>
+    <t>Indexed collections</t>
+  </si>
+  <si>
+    <t>Keyed collections</t>
+  </si>
+  <si>
+    <t>Working with objects</t>
+  </si>
+  <si>
+    <t>Details of the object model</t>
+  </si>
+  <si>
+    <t>Using promises</t>
+  </si>
+  <si>
+    <t>Iterators and generators</t>
+  </si>
+  <si>
+    <t>Meta programming</t>
+  </si>
+  <si>
+    <t>JavaScript modules</t>
+  </si>
+  <si>
+    <t>Client-side JavaScript frameworks</t>
+  </si>
+  <si>
+    <t>Client-side web APIs</t>
+  </si>
+  <si>
+    <t>A re-introduction to JavaScript</t>
+  </si>
+  <si>
+    <t>JavaScript data structures</t>
+  </si>
+  <si>
+    <t>Equality comparisons and sameness</t>
+  </si>
+  <si>
+    <t>Closures</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>Inheritance and the prototype chain</t>
+  </si>
+  <si>
+    <t>Strict mode</t>
+  </si>
+  <si>
+    <t>JavaScript typed arrays</t>
+  </si>
+  <si>
+    <t>Memory Management</t>
+  </si>
+  <si>
+    <t>Concurrency model and Event Loop</t>
+  </si>
+  <si>
+    <t>Build that App (Node.js)</t>
+  </si>
+  <si>
+    <t>NodeJS REST API: Super Simple Setup - Express &amp; NPM (Ep1)</t>
+  </si>
+  <si>
+    <t>NodeJS REST API: Connecting to MySQL (Ep 2)</t>
+  </si>
+  <si>
+    <t>NodeJS REST: Serve HTML Files and POST Requests (Ep 3)</t>
+  </si>
+  <si>
+    <t>NodeJS REST: Refactor Code into Multiple Files  (Ep 4)</t>
+  </si>
+  <si>
+    <t>NodeJS Deploy to Cloud using Heroku (Ep 5)</t>
+  </si>
+  <si>
+    <t>RESTful API Using Node, Express and MongoDB</t>
   </si>
 </sst>
 </file>
@@ -916,7 +1018,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1045,11 +1147,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1116,12 +1229,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2249,21 +2364,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="G1" s="31" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="G1" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="J1" s="31" t="s">
+      <c r="H1" s="32"/>
+      <c r="J1" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="K1" s="31"/>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -2975,22 +3090,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="F1" s="31" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="F1" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="J1" s="31" t="s">
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="J1" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -3938,141 +4053,165 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="C2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="C3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="C4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="C6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="C7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>265</v>
-      </c>
-      <c r="C9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="C10" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="C11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="C12" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="23" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>274</v>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="30" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="27" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4083,6 +4222,286 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="65.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1"/>
+      <c r="C1" s="31" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="33"/>
+      <c r="C28" s="30" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="31" t="s">
+        <v>311</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="27" t="s">
+        <v>316</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Master- To Do.xlsx
+++ b/Master- To Do.xlsx
@@ -9,16 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="5475" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="5475"/>
   </bookViews>
   <sheets>
-    <sheet name="Reading" sheetId="1" r:id="rId1"/>
-    <sheet name="Leetcode" sheetId="2" r:id="rId2"/>
-    <sheet name="Python Node" sheetId="4" r:id="rId3"/>
-    <sheet name="Java" sheetId="6" r:id="rId4"/>
-    <sheet name="JavaScript" sheetId="11" r:id="rId5"/>
-    <sheet name="Tutorial" sheetId="9" r:id="rId6"/>
-    <sheet name="Career" sheetId="7" r:id="rId7"/>
+    <sheet name="Master- Leetcode" sheetId="12" r:id="rId1"/>
+    <sheet name="Reading" sheetId="1" r:id="rId2"/>
+    <sheet name="Leetcode" sheetId="2" r:id="rId3"/>
+    <sheet name="Python Node" sheetId="4" r:id="rId4"/>
+    <sheet name="Java" sheetId="6" r:id="rId5"/>
+    <sheet name="JavaScript" sheetId="11" r:id="rId6"/>
+    <sheet name="Tutorial" sheetId="9" r:id="rId7"/>
+    <sheet name="Career" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="320">
   <si>
     <t>Building Secure and Reliable Systems</t>
   </si>
@@ -984,6 +985,12 @@
   </si>
   <si>
     <t>RESTful API Using Node, Express and MongoDB</t>
+  </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1233,10 +1240,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1517,6 +1525,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2024,7 +2054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2351,7 +2381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2364,21 +2394,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="G1" s="32" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="G1" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="H1" s="32"/>
-      <c r="J1" s="32" t="s">
+      <c r="H1" s="33"/>
+      <c r="J1" s="33" t="s">
         <v>250</v>
       </c>
-      <c r="K1" s="32"/>
+      <c r="K1" s="33"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -3078,7 +3108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3090,22 +3120,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="F1" s="32" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="F1" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="J1" s="32" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="J1" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -4051,7 +4081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4220,7 +4250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4444,7 +4474,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="32"/>
       <c r="C28" s="30" t="s">
         <v>305</v>
       </c>
@@ -4500,7 +4530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
